--- a/vendor-performance/reporting-and-kpis/vendor-performance-analysis-v1.xlsx
+++ b/vendor-performance/reporting-and-kpis/vendor-performance-analysis-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/vendor-performance/reporting-and-kpis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="499" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47939BEC-1FDD-4B3A-BE9E-CB847018B11D}"/>
+  <xr:revisionPtr revIDLastSave="549" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EFD6302-872B-4364-8A3C-6ADD7FCA3636}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -28,10 +28,10 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId7"/>
-    <pivotCache cacheId="13" r:id="rId8"/>
-    <pivotCache cacheId="14" r:id="rId9"/>
-    <pivotCache cacheId="15" r:id="rId10"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="2" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -933,7 +933,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -950,183 +950,220 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 4" xfId="1" builtinId="19"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+  <dxfs count="135">
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1156,6 +1193,815 @@
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1226,9 +2072,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
@@ -1255,6 +2098,9 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
     </dxf>
     <dxf>
       <fill>
@@ -2117,7 +2963,127 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E350ABE4-D46D-497E-8589-6F544B57D953}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{429AB0FC-DE18-4F09-B76F-AF9B4CD91218}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="SLA Status">
+  <location ref="D4:E7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count" fld="7" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="15">
+    <format dxfId="117">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="116">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="115">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="114">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="59">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E350ABE4-D46D-497E-8589-6F544B57D953}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
   <location ref="A4:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -2169,18 +3135,52 @@
   <dataFields count="1">
     <dataField name="Count" fld="9" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="4">
-    <format dxfId="54">
+  <formats count="12">
+    <format dxfId="121">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="120">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="119">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="118">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="64">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2195,8 +3195,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A3941DC-48F8-4608-975F-C9C02236DD79}" name="PivotTable5" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Severity Level">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A3941DC-48F8-4608-975F-C9C02236DD79}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Severity Level">
   <location ref="D13:E17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -2248,18 +3248,56 @@
   <dataFields count="1">
     <dataField name="Count" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="4">
-    <format dxfId="58">
+  <formats count="14">
+    <format dxfId="125">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="124">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="123">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="122">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2274,8 +3312,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7411F72-9E73-47E6-8287-21A4762EAC9D}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Action Status">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7411F72-9E73-47E6-8287-21A4762EAC9D}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Action Status">
   <location ref="A23:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -2323,25 +3361,63 @@
   <dataFields count="1">
     <dataField name="Count" fld="3" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="5">
-    <format dxfId="63">
+  <formats count="15">
+    <format dxfId="130">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="129">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="61">
+    <format dxfId="128">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="127">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="126">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
+    </format>
+    <format dxfId="41">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="40">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2356,8 +3432,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0482F12C-360C-4E28-AAA3-67A087A2BE7A}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Risk Tier">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0482F12C-360C-4E28-AAA3-67A087A2BE7A}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Risk Tier">
   <location ref="A13:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -2403,91 +3479,56 @@
   <dataFields count="1">
     <dataField name="Count" fld="5" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="4">
-    <format dxfId="67">
+  <formats count="14">
+    <format dxfId="134">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="66">
+    <format dxfId="133">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="132">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="64">
+    <format dxfId="131">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{429AB0FC-DE18-4F09-B76F-AF9B4CD91218}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="SLA Status">
-  <location ref="D4:E7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count" fld="7" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="71">
-      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="70">
+    <format dxfId="53">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="69">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="68">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    <format dxfId="32">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2603,15 +3644,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{87A25AAC-9F37-4256-A93E-80C0D761A2B9}" name="Table5" displayName="Table5" ref="D23:F28" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{87A25AAC-9F37-4256-A93E-80C0D761A2B9}" name="Table5" displayName="Table5" ref="D23:F28" totalsRowShown="0" headerRowDxfId="113" dataDxfId="112" tableBorderDxfId="10">
   <autoFilter ref="D23:F28" xr:uid="{87A25AAC-9F37-4256-A93E-80C0D761A2B9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D24:F28">
     <sortCondition ref="D23:D28"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{87F925ED-EE34-4DFE-9885-9CC1ECC97F59}" name="Operational Area" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{19ED6EA1-7AA2-41B4-BB9E-FEBC4DE99056}" name="Confidence Level" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{6433AD34-AE9A-4CBA-A8FE-56A104AEABDA}" name="Primary Reliability Concern" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{87F925ED-EE34-4DFE-9885-9CC1ECC97F59}" name="Operational Area" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{19ED6EA1-7AA2-41B4-BB9E-FEBC4DE99056}" name="Confidence Level" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{6433AD34-AE9A-4CBA-A8FE-56A104AEABDA}" name="Primary Reliability Concern" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2621,17 +3662,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4182B0EF-3BA1-405E-875F-E809D82E9E27}" name="vendor_master" displayName="vendor_master" ref="A1:K13" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K13" xr:uid="{4182B0EF-3BA1-405E-875F-E809D82E9E27}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{26A576E8-0F05-4B3F-8F70-376CDC7620AC}" uniqueName="1" name="vendor_id" queryTableFieldId="1" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{C7C4AA2A-0E5C-4DB8-9D78-1D3C9DA3AA8A}" uniqueName="2" name="vendor_name" queryTableFieldId="2" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{9E6C9575-2450-4157-8293-257ABAEA4D01}" uniqueName="3" name="vendor_type" queryTableFieldId="3" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{490B0ABC-53D7-4615-8B31-ACCB180D73BC}" uniqueName="4" name="primary_service_category" queryTableFieldId="4" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{5987D722-2743-4AAF-9DF2-9234FF22BAB0}" uniqueName="5" name="support_level" queryTableFieldId="5" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{E3B18031-D4E9-4BA7-8D58-126808C660B3}" uniqueName="6" name="risk_tier" queryTableFieldId="6" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{26A576E8-0F05-4B3F-8F70-376CDC7620AC}" uniqueName="1" name="vendor_id" queryTableFieldId="1" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{C7C4AA2A-0E5C-4DB8-9D78-1D3C9DA3AA8A}" uniqueName="2" name="vendor_name" queryTableFieldId="2" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{9E6C9575-2450-4157-8293-257ABAEA4D01}" uniqueName="3" name="vendor_type" queryTableFieldId="3" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{490B0ABC-53D7-4615-8B31-ACCB180D73BC}" uniqueName="4" name="primary_service_category" queryTableFieldId="4" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{5987D722-2743-4AAF-9DF2-9234FF22BAB0}" uniqueName="5" name="support_level" queryTableFieldId="5" dataDxfId="107"/>
+    <tableColumn id="6" xr3:uid="{E3B18031-D4E9-4BA7-8D58-126808C660B3}" uniqueName="6" name="risk_tier" queryTableFieldId="6" dataDxfId="106"/>
     <tableColumn id="7" xr3:uid="{8AD47555-E87F-46E0-A31F-5D5F8DCEADF2}" uniqueName="7" name="preferred_vendor_flag" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{94E68636-7C72-4138-87F6-F26BA45BB93F}" uniqueName="8" name="emergency_fulfillment_flag" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{800E8777-FE01-4128-BD35-3343C6E19D27}" uniqueName="9" name="active_vendor_flag" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{0AFADCB4-BA5F-4A9E-B3CD-545A663A70BC}" uniqueName="10" name="primary_contact_team" queryTableFieldId="10" dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{E153FFBA-5CF9-4394-B722-0957A92C5F4F}" uniqueName="11" name="notes" queryTableFieldId="11" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{0AFADCB4-BA5F-4A9E-B3CD-545A663A70BC}" uniqueName="10" name="primary_contact_team" queryTableFieldId="10" dataDxfId="105"/>
+    <tableColumn id="11" xr3:uid="{E153FFBA-5CF9-4394-B722-0957A92C5F4F}" uniqueName="11" name="notes" queryTableFieldId="11" dataDxfId="104"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2641,16 +3682,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{46B3BAD5-670F-40C8-BCE4-966946BCDCEA}" name="vendor_fulfillment_events" displayName="vendor_fulfillment_events" ref="A1:U7" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:U7" xr:uid="{46B3BAD5-670F-40C8-BCE4-966946BCDCEA}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{291FACAA-D44B-416E-955C-549EE59C671C}" uniqueName="1" name="fulfillment_event_id" queryTableFieldId="1" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{855B7CF0-7D36-4F60-9756-85E4671C9296}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{AD0EC168-4A9D-4882-B03D-B53B53CB610F}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{5820514A-0CAF-4262-A0BE-73482816F0DA}" uniqueName="4" name="item_id" queryTableFieldId="4" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{295490EA-DF07-4145-B1BE-A1A3FE859EBF}" uniqueName="5" name="location_id" queryTableFieldId="5" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{344ADC37-EA88-4BB0-B15A-7A2AF8679AAF}" uniqueName="6" name="order_date" queryTableFieldId="6" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{D8916FC1-2727-4A5A-97EA-FFBBCB33041C}" uniqueName="7" name="expected_delivery_date" queryTableFieldId="7" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{822531DD-3EBE-4589-9205-A532FBCAE1E9}" uniqueName="8" name="actual_delivery_date" queryTableFieldId="8" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{CE0C0425-9B8D-4E34-ADD8-5F3D7D01B23B}" uniqueName="9" name="delivery_status" queryTableFieldId="9" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{21109B24-7923-42A2-9CDA-D86221E98067}" uniqueName="10" name="fulfillment_status" queryTableFieldId="10" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{291FACAA-D44B-416E-955C-549EE59C671C}" uniqueName="1" name="fulfillment_event_id" queryTableFieldId="1" dataDxfId="103"/>
+    <tableColumn id="2" xr3:uid="{855B7CF0-7D36-4F60-9756-85E4671C9296}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{AD0EC168-4A9D-4882-B03D-B53B53CB610F}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{5820514A-0CAF-4262-A0BE-73482816F0DA}" uniqueName="4" name="item_id" queryTableFieldId="4" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{295490EA-DF07-4145-B1BE-A1A3FE859EBF}" uniqueName="5" name="location_id" queryTableFieldId="5" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{344ADC37-EA88-4BB0-B15A-7A2AF8679AAF}" uniqueName="6" name="order_date" queryTableFieldId="6" dataDxfId="98"/>
+    <tableColumn id="7" xr3:uid="{D8916FC1-2727-4A5A-97EA-FFBBCB33041C}" uniqueName="7" name="expected_delivery_date" queryTableFieldId="7" dataDxfId="97"/>
+    <tableColumn id="8" xr3:uid="{822531DD-3EBE-4589-9205-A532FBCAE1E9}" uniqueName="8" name="actual_delivery_date" queryTableFieldId="8" dataDxfId="96"/>
+    <tableColumn id="9" xr3:uid="{CE0C0425-9B8D-4E34-ADD8-5F3D7D01B23B}" uniqueName="9" name="delivery_status" queryTableFieldId="9" dataDxfId="95"/>
+    <tableColumn id="10" xr3:uid="{21109B24-7923-42A2-9CDA-D86221E98067}" uniqueName="10" name="fulfillment_status" queryTableFieldId="10" dataDxfId="94"/>
     <tableColumn id="11" xr3:uid="{30BD8C4C-C932-4824-A068-31857B85FC9E}" uniqueName="11" name="expected_quantity" queryTableFieldId="11"/>
     <tableColumn id="12" xr3:uid="{A0963C35-0DFA-4F7F-9B09-97A0CD817C9B}" uniqueName="12" name="received_quantity" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{8409D753-7A4E-424B-86DA-57E9B66B6902}" uniqueName="13" name="fulfillment_accuracy_flag" queryTableFieldId="13"/>
@@ -2658,10 +3699,10 @@
     <tableColumn id="15" xr3:uid="{45074077-5EAE-47C1-8455-08D55FD11808}" uniqueName="15" name="delay_days" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{FA99FB5B-0907-4A65-9616-A7BF4BC423FD}" uniqueName="16" name="partial_fulfillment_flag" queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{49557976-2516-406C-A11F-89FEB28E231A}" uniqueName="17" name="emergency_fulfillment_flag" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{517B1408-EC5A-45C4-AD99-3AA660BB3867}" uniqueName="18" name="operational_impact_level" queryTableFieldId="18" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{517B1408-EC5A-45C4-AD99-3AA660BB3867}" uniqueName="18" name="operational_impact_level" queryTableFieldId="18" dataDxfId="93"/>
     <tableColumn id="19" xr3:uid="{670858BE-FAC2-4FDE-A882-5FD510B11B06}" uniqueName="19" name="escalation_required_flag" queryTableFieldId="19"/>
-    <tableColumn id="20" xr3:uid="{0B8A4F43-1F4D-4B16-9777-309614CA9FC9}" uniqueName="20" name="related_ticket_id" queryTableFieldId="20" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{D38A904B-6B86-4A3A-8271-A2E7A3CB843E}" uniqueName="21" name="notes" queryTableFieldId="21" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{0B8A4F43-1F4D-4B16-9777-309614CA9FC9}" uniqueName="20" name="related_ticket_id" queryTableFieldId="20" dataDxfId="92"/>
+    <tableColumn id="21" xr3:uid="{D38A904B-6B86-4A3A-8271-A2E7A3CB843E}" uniqueName="21" name="notes" queryTableFieldId="21" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2671,21 +3712,21 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{000F99B4-8EF9-4D5E-8ED8-8572F424D91B}" name="vendor_sla_tracking" displayName="vendor_sla_tracking" ref="A1:O7" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:O7" xr:uid="{000F99B4-8EF9-4D5E-8ED8-8572F424D91B}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{BAA272D0-48DE-4FE4-A55E-CB38B511F8E1}" uniqueName="1" name="sla_event_id" queryTableFieldId="1" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{36A04F74-04D5-408A-AB94-80E9BF8DB59E}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{B2304B79-7526-4BD8-9718-698F8D7B20B1}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{A3DF195D-D536-4302-B936-2E0901FC45D4}" uniqueName="4" name="fulfillment_event_id" queryTableFieldId="4" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{BF918E9E-4B17-4441-A493-F418306E6685}" uniqueName="5" name="sla_category" queryTableFieldId="5" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{BAA272D0-48DE-4FE4-A55E-CB38B511F8E1}" uniqueName="1" name="sla_event_id" queryTableFieldId="1" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{36A04F74-04D5-408A-AB94-80E9BF8DB59E}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{B2304B79-7526-4BD8-9718-698F8D7B20B1}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{A3DF195D-D536-4302-B936-2E0901FC45D4}" uniqueName="4" name="fulfillment_event_id" queryTableFieldId="4" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{BF918E9E-4B17-4441-A493-F418306E6685}" uniqueName="5" name="sla_category" queryTableFieldId="5" dataDxfId="86"/>
     <tableColumn id="6" xr3:uid="{EEE95176-80E1-4B5E-8802-818334596381}" uniqueName="6" name="sla_target_hours" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{31DDA0AF-D7C2-4799-BC6F-41FB14E9CA73}" uniqueName="7" name="actual_response_hours" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{3C54470B-3D86-4470-85B6-E7D008CE91EB}" uniqueName="8" name="sla_status" queryTableFieldId="8" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{3C54470B-3D86-4470-85B6-E7D008CE91EB}" uniqueName="8" name="sla_status" queryTableFieldId="8" dataDxfId="85"/>
     <tableColumn id="9" xr3:uid="{8C4C7C05-BAF3-49EF-A3F8-24FB6AEF2814}" uniqueName="9" name="sla_breach_flag" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{C61E5816-17DE-47DF-844D-EAF8F40FDD01}" uniqueName="10" name="escalation_required_flag" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{806B9CEE-F7EF-4A8C-B0A9-97AC93EE1A4E}" uniqueName="11" name="operational_impact_level" queryTableFieldId="11" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{74A1377D-C647-408A-9AEF-E4633B496D12}" uniqueName="12" name="related_ticket_id" queryTableFieldId="12" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{A2AE87D3-8E7A-424F-ADC7-402B2967A04A}" uniqueName="13" name="review_date" queryTableFieldId="13" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{806B9CEE-F7EF-4A8C-B0A9-97AC93EE1A4E}" uniqueName="11" name="operational_impact_level" queryTableFieldId="11" dataDxfId="84"/>
+    <tableColumn id="12" xr3:uid="{74A1377D-C647-408A-9AEF-E4633B496D12}" uniqueName="12" name="related_ticket_id" queryTableFieldId="12" dataDxfId="83"/>
+    <tableColumn id="13" xr3:uid="{A2AE87D3-8E7A-424F-ADC7-402B2967A04A}" uniqueName="13" name="review_date" queryTableFieldId="13" dataDxfId="82"/>
     <tableColumn id="14" xr3:uid="{B39E41F9-6277-4EA4-AB31-76BFB8A06B5C}" uniqueName="14" name="corrective_action_required_flag" queryTableFieldId="14"/>
-    <tableColumn id="15" xr3:uid="{53F3DC06-75A0-4F70-AAAA-3C2E2ED3E3CF}" uniqueName="15" name="notes" queryTableFieldId="15" dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{53F3DC06-75A0-4F70-AAAA-3C2E2ED3E3CF}" uniqueName="15" name="notes" queryTableFieldId="15" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2695,23 +3736,23 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F83C8A38-7930-4A65-BC92-DC4CEE03691F}" name="vendor_corrective_actions" displayName="vendor_corrective_actions" ref="A1:Q6" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Q6" xr:uid="{F83C8A38-7930-4A65-BC92-DC4CEE03691F}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{94393011-C2A5-4543-82E0-CF2CFFCC768E}" uniqueName="1" name="corrective_action_id" queryTableFieldId="1" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{FE31803A-AA27-4B50-A5D7-2E933EED8EDD}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{322B6FC8-D1D5-4475-BE8F-15A61EBA326A}" uniqueName="3" name="corrective_action_type" queryTableFieldId="3" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{CFCC0F4F-9C54-4E9B-8154-D94CF415DABC}" uniqueName="4" name="corrective_action_status" queryTableFieldId="4" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{D9F65932-2450-46D1-BA75-E97239AFB3A2}" uniqueName="5" name="corrective_action_severity" queryTableFieldId="5" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{3D6348E0-F229-42E7-8BC6-25410ABC533F}" uniqueName="6" name="trigger_reason" queryTableFieldId="6" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{A991BE3E-58DC-4413-AFB9-682D257B02E8}" uniqueName="7" name="sla_event_id" queryTableFieldId="7" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{938AAB17-52F3-454A-8E39-162FCA9BCF8C}" uniqueName="8" name="fulfillment_event_id" queryTableFieldId="8" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{F056C6FD-A1B5-4A50-8438-86C2DD40520A}" uniqueName="9" name="related_ticket_id" queryTableFieldId="9" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{11697B55-AB9D-454C-8691-BF5BE47BEB60}" uniqueName="10" name="assigned_owner" queryTableFieldId="10" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{38AB43C5-F50C-4381-9C00-EB47F455F7F4}" uniqueName="11" name="remediation_plan_summary" queryTableFieldId="11" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{870C00F8-318D-45DA-ADDB-D9B98F6B628D}" uniqueName="12" name="monitoring_start_date" queryTableFieldId="12" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{11B305D6-D59B-4D19-B2F2-D454A113338E}" uniqueName="13" name="reassessment_date" queryTableFieldId="13" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{2949F919-CB24-4681-8F68-4D56AA038F20}" uniqueName="14" name="recovery_status" queryTableFieldId="14" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{94393011-C2A5-4543-82E0-CF2CFFCC768E}" uniqueName="1" name="corrective_action_id" queryTableFieldId="1" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{FE31803A-AA27-4B50-A5D7-2E933EED8EDD}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{322B6FC8-D1D5-4475-BE8F-15A61EBA326A}" uniqueName="3" name="corrective_action_type" queryTableFieldId="3" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{CFCC0F4F-9C54-4E9B-8154-D94CF415DABC}" uniqueName="4" name="corrective_action_status" queryTableFieldId="4" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{D9F65932-2450-46D1-BA75-E97239AFB3A2}" uniqueName="5" name="corrective_action_severity" queryTableFieldId="5" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{3D6348E0-F229-42E7-8BC6-25410ABC533F}" uniqueName="6" name="trigger_reason" queryTableFieldId="6" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{A991BE3E-58DC-4413-AFB9-682D257B02E8}" uniqueName="7" name="sla_event_id" queryTableFieldId="7" dataDxfId="74"/>
+    <tableColumn id="8" xr3:uid="{938AAB17-52F3-454A-8E39-162FCA9BCF8C}" uniqueName="8" name="fulfillment_event_id" queryTableFieldId="8" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{F056C6FD-A1B5-4A50-8438-86C2DD40520A}" uniqueName="9" name="related_ticket_id" queryTableFieldId="9" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{11697B55-AB9D-454C-8691-BF5BE47BEB60}" uniqueName="10" name="assigned_owner" queryTableFieldId="10" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{38AB43C5-F50C-4381-9C00-EB47F455F7F4}" uniqueName="11" name="remediation_plan_summary" queryTableFieldId="11" dataDxfId="70"/>
+    <tableColumn id="12" xr3:uid="{870C00F8-318D-45DA-ADDB-D9B98F6B628D}" uniqueName="12" name="monitoring_start_date" queryTableFieldId="12" dataDxfId="69"/>
+    <tableColumn id="13" xr3:uid="{11B305D6-D59B-4D19-B2F2-D454A113338E}" uniqueName="13" name="reassessment_date" queryTableFieldId="13" dataDxfId="68"/>
+    <tableColumn id="14" xr3:uid="{2949F919-CB24-4681-8F68-4D56AA038F20}" uniqueName="14" name="recovery_status" queryTableFieldId="14" dataDxfId="67"/>
     <tableColumn id="15" xr3:uid="{6B20598D-F079-488D-9D7B-03C45D65B7FC}" uniqueName="15" name="escalation_required_flag" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{25BED46A-F022-4F67-9E00-3626A945389F}" uniqueName="16" name="corrective_action_closed_flag" queryTableFieldId="16"/>
-    <tableColumn id="17" xr3:uid="{BAE5645A-C5DF-476C-9271-E06114098F21}" uniqueName="17" name="notes" queryTableFieldId="17" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{BAE5645A-C5DF-476C-9271-E06114098F21}" uniqueName="17" name="notes" queryTableFieldId="17" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2987,32 +4028,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="7" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="8" t="s">
         <v>231</v>
       </c>
     </row>
@@ -3036,9 +4077,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="21" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="8" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3062,9 +4103,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="34" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="8" t="s">
         <v>233</v>
       </c>
     </row>
@@ -3083,9 +4124,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="45" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="8" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3109,7 +4150,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="58" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3122,7 +4163,7 @@
   <cols>
     <col min="1" max="1" width="35.5703125" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="47.140625" customWidth="1"/>
@@ -3131,280 +4172,302 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="25"/>
+      <c r="D3" s="24" t="s">
         <v>198</v>
       </c>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="14">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="14">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="17">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="3" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="8" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="25"/>
+      <c r="D12" s="24" t="s">
         <v>202</v>
       </c>
+      <c r="E12" s="25"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="14">
         <v>5</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="3" customFormat="1" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="31"/>
+      <c r="B18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="15" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="25"/>
+      <c r="D22" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="27" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="19">
         <v>1</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="28" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="19">
         <v>2</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="28" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="21">
         <v>2</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="28" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="B27"/>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="28" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="7" t="s">
+    <row r="28" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="23" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+    </row>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>

--- a/vendor-performance/reporting-and-kpis/vendor-performance-analysis-v1.xlsx
+++ b/vendor-performance/reporting-and-kpis/vendor-performance-analysis-v1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="549" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EFD6302-872B-4364-8A3C-6ADD7FCA3636}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2985" yWindow="2985" windowWidth="23475" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -1115,7 +1115,7 @@
     <cellStyle name="Heading 4" xfId="1" builtinId="19"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="135">
+  <dxfs count="122">
     <dxf>
       <border>
         <bottom style="thin">
@@ -1128,27 +1128,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -1346,121 +1325,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3010,54 +2874,54 @@
     <dataField name="Count" fld="7" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="117">
+    <format dxfId="104">
       <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="116">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="115">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="114">
+    <format dxfId="101">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="47">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="45">
       <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="20">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="18">
       <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="0">
@@ -3136,41 +3000,41 @@
     <dataField name="Count" fld="9" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="121">
+    <format dxfId="108">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="120">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="119">
+    <format dxfId="106">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="118">
+    <format dxfId="105">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="52">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="64">
+    <format dxfId="51">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="50">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="27">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="1">
@@ -3249,54 +3113,54 @@
     <dataField name="Count" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="125">
+    <format dxfId="112">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="124">
+    <format dxfId="111">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="123">
+    <format dxfId="110">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="122">
+    <format dxfId="109">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="37">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="35">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="15">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="13">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3362,61 +3226,61 @@
     <dataField name="Count" fld="3" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="130">
+    <format dxfId="117">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="129">
+    <format dxfId="116">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="115">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="127">
+    <format dxfId="114">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="126">
+    <format dxfId="113">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="32">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="31">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="30">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="10">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="3">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3480,54 +3344,54 @@
     <dataField name="Count" fld="5" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="134">
+    <format dxfId="121">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="120">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="132">
+    <format dxfId="119">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="131">
+    <format dxfId="118">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="42">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="40">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="25">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="23">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3644,15 +3508,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{87A25AAC-9F37-4256-A93E-80C0D761A2B9}" name="Table5" displayName="Table5" ref="D23:F28" totalsRowShown="0" headerRowDxfId="113" dataDxfId="112" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{87A25AAC-9F37-4256-A93E-80C0D761A2B9}" name="Table5" displayName="Table5" ref="D23:F28" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99" tableBorderDxfId="7">
   <autoFilter ref="D23:F28" xr:uid="{87A25AAC-9F37-4256-A93E-80C0D761A2B9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D24:F28">
     <sortCondition ref="D23:D28"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{87F925ED-EE34-4DFE-9885-9CC1ECC97F59}" name="Operational Area" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{19ED6EA1-7AA2-41B4-BB9E-FEBC4DE99056}" name="Confidence Level" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{6433AD34-AE9A-4CBA-A8FE-56A104AEABDA}" name="Primary Reliability Concern" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{87F925ED-EE34-4DFE-9885-9CC1ECC97F59}" name="Operational Area" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{19ED6EA1-7AA2-41B4-BB9E-FEBC4DE99056}" name="Confidence Level" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{6433AD34-AE9A-4CBA-A8FE-56A104AEABDA}" name="Primary Reliability Concern" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3662,17 +3526,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4182B0EF-3BA1-405E-875F-E809D82E9E27}" name="vendor_master" displayName="vendor_master" ref="A1:K13" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K13" xr:uid="{4182B0EF-3BA1-405E-875F-E809D82E9E27}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{26A576E8-0F05-4B3F-8F70-376CDC7620AC}" uniqueName="1" name="vendor_id" queryTableFieldId="1" dataDxfId="111"/>
-    <tableColumn id="2" xr3:uid="{C7C4AA2A-0E5C-4DB8-9D78-1D3C9DA3AA8A}" uniqueName="2" name="vendor_name" queryTableFieldId="2" dataDxfId="110"/>
-    <tableColumn id="3" xr3:uid="{9E6C9575-2450-4157-8293-257ABAEA4D01}" uniqueName="3" name="vendor_type" queryTableFieldId="3" dataDxfId="109"/>
-    <tableColumn id="4" xr3:uid="{490B0ABC-53D7-4615-8B31-ACCB180D73BC}" uniqueName="4" name="primary_service_category" queryTableFieldId="4" dataDxfId="108"/>
-    <tableColumn id="5" xr3:uid="{5987D722-2743-4AAF-9DF2-9234FF22BAB0}" uniqueName="5" name="support_level" queryTableFieldId="5" dataDxfId="107"/>
-    <tableColumn id="6" xr3:uid="{E3B18031-D4E9-4BA7-8D58-126808C660B3}" uniqueName="6" name="risk_tier" queryTableFieldId="6" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{26A576E8-0F05-4B3F-8F70-376CDC7620AC}" uniqueName="1" name="vendor_id" queryTableFieldId="1" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{C7C4AA2A-0E5C-4DB8-9D78-1D3C9DA3AA8A}" uniqueName="2" name="vendor_name" queryTableFieldId="2" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{9E6C9575-2450-4157-8293-257ABAEA4D01}" uniqueName="3" name="vendor_type" queryTableFieldId="3" dataDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{490B0ABC-53D7-4615-8B31-ACCB180D73BC}" uniqueName="4" name="primary_service_category" queryTableFieldId="4" dataDxfId="95"/>
+    <tableColumn id="5" xr3:uid="{5987D722-2743-4AAF-9DF2-9234FF22BAB0}" uniqueName="5" name="support_level" queryTableFieldId="5" dataDxfId="94"/>
+    <tableColumn id="6" xr3:uid="{E3B18031-D4E9-4BA7-8D58-126808C660B3}" uniqueName="6" name="risk_tier" queryTableFieldId="6" dataDxfId="93"/>
     <tableColumn id="7" xr3:uid="{8AD47555-E87F-46E0-A31F-5D5F8DCEADF2}" uniqueName="7" name="preferred_vendor_flag" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{94E68636-7C72-4138-87F6-F26BA45BB93F}" uniqueName="8" name="emergency_fulfillment_flag" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{800E8777-FE01-4128-BD35-3343C6E19D27}" uniqueName="9" name="active_vendor_flag" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{0AFADCB4-BA5F-4A9E-B3CD-545A663A70BC}" uniqueName="10" name="primary_contact_team" queryTableFieldId="10" dataDxfId="105"/>
-    <tableColumn id="11" xr3:uid="{E153FFBA-5CF9-4394-B722-0957A92C5F4F}" uniqueName="11" name="notes" queryTableFieldId="11" dataDxfId="104"/>
+    <tableColumn id="10" xr3:uid="{0AFADCB4-BA5F-4A9E-B3CD-545A663A70BC}" uniqueName="10" name="primary_contact_team" queryTableFieldId="10" dataDxfId="92"/>
+    <tableColumn id="11" xr3:uid="{E153FFBA-5CF9-4394-B722-0957A92C5F4F}" uniqueName="11" name="notes" queryTableFieldId="11" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3682,16 +3546,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{46B3BAD5-670F-40C8-BCE4-966946BCDCEA}" name="vendor_fulfillment_events" displayName="vendor_fulfillment_events" ref="A1:U7" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:U7" xr:uid="{46B3BAD5-670F-40C8-BCE4-966946BCDCEA}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{291FACAA-D44B-416E-955C-549EE59C671C}" uniqueName="1" name="fulfillment_event_id" queryTableFieldId="1" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{855B7CF0-7D36-4F60-9756-85E4671C9296}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{AD0EC168-4A9D-4882-B03D-B53B53CB610F}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="101"/>
-    <tableColumn id="4" xr3:uid="{5820514A-0CAF-4262-A0BE-73482816F0DA}" uniqueName="4" name="item_id" queryTableFieldId="4" dataDxfId="100"/>
-    <tableColumn id="5" xr3:uid="{295490EA-DF07-4145-B1BE-A1A3FE859EBF}" uniqueName="5" name="location_id" queryTableFieldId="5" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{344ADC37-EA88-4BB0-B15A-7A2AF8679AAF}" uniqueName="6" name="order_date" queryTableFieldId="6" dataDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{D8916FC1-2727-4A5A-97EA-FFBBCB33041C}" uniqueName="7" name="expected_delivery_date" queryTableFieldId="7" dataDxfId="97"/>
-    <tableColumn id="8" xr3:uid="{822531DD-3EBE-4589-9205-A532FBCAE1E9}" uniqueName="8" name="actual_delivery_date" queryTableFieldId="8" dataDxfId="96"/>
-    <tableColumn id="9" xr3:uid="{CE0C0425-9B8D-4E34-ADD8-5F3D7D01B23B}" uniqueName="9" name="delivery_status" queryTableFieldId="9" dataDxfId="95"/>
-    <tableColumn id="10" xr3:uid="{21109B24-7923-42A2-9CDA-D86221E98067}" uniqueName="10" name="fulfillment_status" queryTableFieldId="10" dataDxfId="94"/>
+    <tableColumn id="1" xr3:uid="{291FACAA-D44B-416E-955C-549EE59C671C}" uniqueName="1" name="fulfillment_event_id" queryTableFieldId="1" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{855B7CF0-7D36-4F60-9756-85E4671C9296}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{AD0EC168-4A9D-4882-B03D-B53B53CB610F}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{5820514A-0CAF-4262-A0BE-73482816F0DA}" uniqueName="4" name="item_id" queryTableFieldId="4" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{295490EA-DF07-4145-B1BE-A1A3FE859EBF}" uniqueName="5" name="location_id" queryTableFieldId="5" dataDxfId="86"/>
+    <tableColumn id="6" xr3:uid="{344ADC37-EA88-4BB0-B15A-7A2AF8679AAF}" uniqueName="6" name="order_date" queryTableFieldId="6" dataDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{D8916FC1-2727-4A5A-97EA-FFBBCB33041C}" uniqueName="7" name="expected_delivery_date" queryTableFieldId="7" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{822531DD-3EBE-4589-9205-A532FBCAE1E9}" uniqueName="8" name="actual_delivery_date" queryTableFieldId="8" dataDxfId="83"/>
+    <tableColumn id="9" xr3:uid="{CE0C0425-9B8D-4E34-ADD8-5F3D7D01B23B}" uniqueName="9" name="delivery_status" queryTableFieldId="9" dataDxfId="82"/>
+    <tableColumn id="10" xr3:uid="{21109B24-7923-42A2-9CDA-D86221E98067}" uniqueName="10" name="fulfillment_status" queryTableFieldId="10" dataDxfId="81"/>
     <tableColumn id="11" xr3:uid="{30BD8C4C-C932-4824-A068-31857B85FC9E}" uniqueName="11" name="expected_quantity" queryTableFieldId="11"/>
     <tableColumn id="12" xr3:uid="{A0963C35-0DFA-4F7F-9B09-97A0CD817C9B}" uniqueName="12" name="received_quantity" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{8409D753-7A4E-424B-86DA-57E9B66B6902}" uniqueName="13" name="fulfillment_accuracy_flag" queryTableFieldId="13"/>
@@ -3699,10 +3563,10 @@
     <tableColumn id="15" xr3:uid="{45074077-5EAE-47C1-8455-08D55FD11808}" uniqueName="15" name="delay_days" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{FA99FB5B-0907-4A65-9616-A7BF4BC423FD}" uniqueName="16" name="partial_fulfillment_flag" queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{49557976-2516-406C-A11F-89FEB28E231A}" uniqueName="17" name="emergency_fulfillment_flag" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{517B1408-EC5A-45C4-AD99-3AA660BB3867}" uniqueName="18" name="operational_impact_level" queryTableFieldId="18" dataDxfId="93"/>
+    <tableColumn id="18" xr3:uid="{517B1408-EC5A-45C4-AD99-3AA660BB3867}" uniqueName="18" name="operational_impact_level" queryTableFieldId="18" dataDxfId="80"/>
     <tableColumn id="19" xr3:uid="{670858BE-FAC2-4FDE-A882-5FD510B11B06}" uniqueName="19" name="escalation_required_flag" queryTableFieldId="19"/>
-    <tableColumn id="20" xr3:uid="{0B8A4F43-1F4D-4B16-9777-309614CA9FC9}" uniqueName="20" name="related_ticket_id" queryTableFieldId="20" dataDxfId="92"/>
-    <tableColumn id="21" xr3:uid="{D38A904B-6B86-4A3A-8271-A2E7A3CB843E}" uniqueName="21" name="notes" queryTableFieldId="21" dataDxfId="91"/>
+    <tableColumn id="20" xr3:uid="{0B8A4F43-1F4D-4B16-9777-309614CA9FC9}" uniqueName="20" name="related_ticket_id" queryTableFieldId="20" dataDxfId="79"/>
+    <tableColumn id="21" xr3:uid="{D38A904B-6B86-4A3A-8271-A2E7A3CB843E}" uniqueName="21" name="notes" queryTableFieldId="21" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3712,21 +3576,21 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{000F99B4-8EF9-4D5E-8ED8-8572F424D91B}" name="vendor_sla_tracking" displayName="vendor_sla_tracking" ref="A1:O7" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:O7" xr:uid="{000F99B4-8EF9-4D5E-8ED8-8572F424D91B}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{BAA272D0-48DE-4FE4-A55E-CB38B511F8E1}" uniqueName="1" name="sla_event_id" queryTableFieldId="1" dataDxfId="90"/>
-    <tableColumn id="2" xr3:uid="{36A04F74-04D5-408A-AB94-80E9BF8DB59E}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="89"/>
-    <tableColumn id="3" xr3:uid="{B2304B79-7526-4BD8-9718-698F8D7B20B1}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="88"/>
-    <tableColumn id="4" xr3:uid="{A3DF195D-D536-4302-B936-2E0901FC45D4}" uniqueName="4" name="fulfillment_event_id" queryTableFieldId="4" dataDxfId="87"/>
-    <tableColumn id="5" xr3:uid="{BF918E9E-4B17-4441-A493-F418306E6685}" uniqueName="5" name="sla_category" queryTableFieldId="5" dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{BAA272D0-48DE-4FE4-A55E-CB38B511F8E1}" uniqueName="1" name="sla_event_id" queryTableFieldId="1" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{36A04F74-04D5-408A-AB94-80E9BF8DB59E}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{B2304B79-7526-4BD8-9718-698F8D7B20B1}" uniqueName="3" name="shipment_id" queryTableFieldId="3" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{A3DF195D-D536-4302-B936-2E0901FC45D4}" uniqueName="4" name="fulfillment_event_id" queryTableFieldId="4" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{BF918E9E-4B17-4441-A493-F418306E6685}" uniqueName="5" name="sla_category" queryTableFieldId="5" dataDxfId="73"/>
     <tableColumn id="6" xr3:uid="{EEE95176-80E1-4B5E-8802-818334596381}" uniqueName="6" name="sla_target_hours" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{31DDA0AF-D7C2-4799-BC6F-41FB14E9CA73}" uniqueName="7" name="actual_response_hours" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{3C54470B-3D86-4470-85B6-E7D008CE91EB}" uniqueName="8" name="sla_status" queryTableFieldId="8" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{3C54470B-3D86-4470-85B6-E7D008CE91EB}" uniqueName="8" name="sla_status" queryTableFieldId="8" dataDxfId="72"/>
     <tableColumn id="9" xr3:uid="{8C4C7C05-BAF3-49EF-A3F8-24FB6AEF2814}" uniqueName="9" name="sla_breach_flag" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{C61E5816-17DE-47DF-844D-EAF8F40FDD01}" uniqueName="10" name="escalation_required_flag" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{806B9CEE-F7EF-4A8C-B0A9-97AC93EE1A4E}" uniqueName="11" name="operational_impact_level" queryTableFieldId="11" dataDxfId="84"/>
-    <tableColumn id="12" xr3:uid="{74A1377D-C647-408A-9AEF-E4633B496D12}" uniqueName="12" name="related_ticket_id" queryTableFieldId="12" dataDxfId="83"/>
-    <tableColumn id="13" xr3:uid="{A2AE87D3-8E7A-424F-ADC7-402B2967A04A}" uniqueName="13" name="review_date" queryTableFieldId="13" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{806B9CEE-F7EF-4A8C-B0A9-97AC93EE1A4E}" uniqueName="11" name="operational_impact_level" queryTableFieldId="11" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{74A1377D-C647-408A-9AEF-E4633B496D12}" uniqueName="12" name="related_ticket_id" queryTableFieldId="12" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{A2AE87D3-8E7A-424F-ADC7-402B2967A04A}" uniqueName="13" name="review_date" queryTableFieldId="13" dataDxfId="69"/>
     <tableColumn id="14" xr3:uid="{B39E41F9-6277-4EA4-AB31-76BFB8A06B5C}" uniqueName="14" name="corrective_action_required_flag" queryTableFieldId="14"/>
-    <tableColumn id="15" xr3:uid="{53F3DC06-75A0-4F70-AAAA-3C2E2ED3E3CF}" uniqueName="15" name="notes" queryTableFieldId="15" dataDxfId="81"/>
+    <tableColumn id="15" xr3:uid="{53F3DC06-75A0-4F70-AAAA-3C2E2ED3E3CF}" uniqueName="15" name="notes" queryTableFieldId="15" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3736,23 +3600,23 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F83C8A38-7930-4A65-BC92-DC4CEE03691F}" name="vendor_corrective_actions" displayName="vendor_corrective_actions" ref="A1:Q6" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Q6" xr:uid="{F83C8A38-7930-4A65-BC92-DC4CEE03691F}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{94393011-C2A5-4543-82E0-CF2CFFCC768E}" uniqueName="1" name="corrective_action_id" queryTableFieldId="1" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{FE31803A-AA27-4B50-A5D7-2E933EED8EDD}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{322B6FC8-D1D5-4475-BE8F-15A61EBA326A}" uniqueName="3" name="corrective_action_type" queryTableFieldId="3" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{CFCC0F4F-9C54-4E9B-8154-D94CF415DABC}" uniqueName="4" name="corrective_action_status" queryTableFieldId="4" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{D9F65932-2450-46D1-BA75-E97239AFB3A2}" uniqueName="5" name="corrective_action_severity" queryTableFieldId="5" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{3D6348E0-F229-42E7-8BC6-25410ABC533F}" uniqueName="6" name="trigger_reason" queryTableFieldId="6" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{A991BE3E-58DC-4413-AFB9-682D257B02E8}" uniqueName="7" name="sla_event_id" queryTableFieldId="7" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{938AAB17-52F3-454A-8E39-162FCA9BCF8C}" uniqueName="8" name="fulfillment_event_id" queryTableFieldId="8" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{F056C6FD-A1B5-4A50-8438-86C2DD40520A}" uniqueName="9" name="related_ticket_id" queryTableFieldId="9" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{11697B55-AB9D-454C-8691-BF5BE47BEB60}" uniqueName="10" name="assigned_owner" queryTableFieldId="10" dataDxfId="71"/>
-    <tableColumn id="11" xr3:uid="{38AB43C5-F50C-4381-9C00-EB47F455F7F4}" uniqueName="11" name="remediation_plan_summary" queryTableFieldId="11" dataDxfId="70"/>
-    <tableColumn id="12" xr3:uid="{870C00F8-318D-45DA-ADDB-D9B98F6B628D}" uniqueName="12" name="monitoring_start_date" queryTableFieldId="12" dataDxfId="69"/>
-    <tableColumn id="13" xr3:uid="{11B305D6-D59B-4D19-B2F2-D454A113338E}" uniqueName="13" name="reassessment_date" queryTableFieldId="13" dataDxfId="68"/>
-    <tableColumn id="14" xr3:uid="{2949F919-CB24-4681-8F68-4D56AA038F20}" uniqueName="14" name="recovery_status" queryTableFieldId="14" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{94393011-C2A5-4543-82E0-CF2CFFCC768E}" uniqueName="1" name="corrective_action_id" queryTableFieldId="1" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{FE31803A-AA27-4B50-A5D7-2E933EED8EDD}" uniqueName="2" name="vendor_id" queryTableFieldId="2" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{322B6FC8-D1D5-4475-BE8F-15A61EBA326A}" uniqueName="3" name="corrective_action_type" queryTableFieldId="3" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{CFCC0F4F-9C54-4E9B-8154-D94CF415DABC}" uniqueName="4" name="corrective_action_status" queryTableFieldId="4" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{D9F65932-2450-46D1-BA75-E97239AFB3A2}" uniqueName="5" name="corrective_action_severity" queryTableFieldId="5" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{3D6348E0-F229-42E7-8BC6-25410ABC533F}" uniqueName="6" name="trigger_reason" queryTableFieldId="6" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{A991BE3E-58DC-4413-AFB9-682D257B02E8}" uniqueName="7" name="sla_event_id" queryTableFieldId="7" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{938AAB17-52F3-454A-8E39-162FCA9BCF8C}" uniqueName="8" name="fulfillment_event_id" queryTableFieldId="8" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{F056C6FD-A1B5-4A50-8438-86C2DD40520A}" uniqueName="9" name="related_ticket_id" queryTableFieldId="9" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{11697B55-AB9D-454C-8691-BF5BE47BEB60}" uniqueName="10" name="assigned_owner" queryTableFieldId="10" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{38AB43C5-F50C-4381-9C00-EB47F455F7F4}" uniqueName="11" name="remediation_plan_summary" queryTableFieldId="11" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{870C00F8-318D-45DA-ADDB-D9B98F6B628D}" uniqueName="12" name="monitoring_start_date" queryTableFieldId="12" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{11B305D6-D59B-4D19-B2F2-D454A113338E}" uniqueName="13" name="reassessment_date" queryTableFieldId="13" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{2949F919-CB24-4681-8F68-4D56AA038F20}" uniqueName="14" name="recovery_status" queryTableFieldId="14" dataDxfId="54"/>
     <tableColumn id="15" xr3:uid="{6B20598D-F079-488D-9D7B-03C45D65B7FC}" uniqueName="15" name="escalation_required_flag" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{25BED46A-F022-4F67-9E00-3626A945389F}" uniqueName="16" name="corrective_action_closed_flag" queryTableFieldId="16"/>
-    <tableColumn id="17" xr3:uid="{BAE5645A-C5DF-476C-9271-E06114098F21}" uniqueName="17" name="notes" queryTableFieldId="17" dataDxfId="66"/>
+    <tableColumn id="17" xr3:uid="{BAE5645A-C5DF-476C-9271-E06114098F21}" uniqueName="17" name="notes" queryTableFieldId="17" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/vendor-performance/reporting-and-kpis/vendor-performance-analysis-v1.xlsx
+++ b/vendor-performance/reporting-and-kpis/vendor-performance-analysis-v1.xlsx
@@ -745,7 +745,7 @@
     <t>Severity Level</t>
   </si>
   <si>
-    <t>Northstar Health Operations</t>
+    <t>Northstar Enterprise</t>
   </si>
   <si>
     <t>Vendor Performance Executive Summary</t>
